--- a/testdata/lead/bulk_upload/vikas_contact.xlsx
+++ b/testdata/lead/bulk_upload/vikas_contact.xlsx
@@ -412,57 +412,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Vedanshi Talwar</v>
+        <v>Bandhu Mukhopadhyay</v>
       </c>
       <c r="B2" t="str">
-        <v>vedanshi.talwar708@gmail.com</v>
+        <v>bandhu.mukhopadhyay389@gmail.com</v>
       </c>
       <c r="C2">
-        <v>9951218500</v>
+        <v>9634599818</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Mangalya Johar</v>
+        <v>Heema Patil</v>
       </c>
       <c r="B3" t="str">
-        <v>mangalya.johar777@gmail.com</v>
+        <v>heema.patil324@gmail.com</v>
       </c>
       <c r="C3">
-        <v>8829242226</v>
+        <v>6339150113</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Akula Iyengar</v>
+        <v>Vimala Bhattacharya</v>
       </c>
       <c r="B4" t="str">
-        <v>akula.iyengar216@gmail.com</v>
+        <v>vimala.bhattacharya882@gmail.com</v>
       </c>
       <c r="C4">
-        <v>9679574362</v>
+        <v>9938496185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Vaijayanti Kapoor</v>
+        <v>Chaturaanan Saini</v>
       </c>
       <c r="B5" t="str">
-        <v>vaijayanti.kapoor458@gmail.com</v>
+        <v>chaturaanan.saini520@gmail.com</v>
       </c>
       <c r="C5">
-        <v>7032756063</v>
+        <v>9912298487</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Manoj Namboothiri</v>
+        <v>Sujata Shah</v>
       </c>
       <c r="B6" t="str">
-        <v>manoj.namboothiri801@gmail.com</v>
+        <v>sujata.shah167@gmail.com</v>
       </c>
       <c r="C6">
-        <v>7983145631</v>
+        <v>9698567782</v>
       </c>
     </row>
   </sheetData>
